--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
@@ -2044,7 +2044,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:55</t>
+    <t xml:space="preserve">2026-09-18 11:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
